--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486261_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486261_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.2111</v>
+        <v>6.2372</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0573</v>
+        <v>6.2376</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1537</v>
+        <v>-0.0004</v>
       </c>
       <c r="G2" t="n">
         <v>4.6681</v>
@@ -610,13 +610,13 @@
         <v>0.435</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3032</v>
+        <v>1.3294</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4831</v>
+        <v>0.6633</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8201000000000001</v>
+        <v>0.666</v>
       </c>
       <c r="V2" t="n">
         <v>-0.1952</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.0507</v>
+        <v>5.8341</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9761</v>
+        <v>3.8211</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0746</v>
+        <v>2.013</v>
       </c>
       <c r="G3" t="n">
         <v>4.5748</v>
@@ -688,13 +688,13 @@
         <v>0.87</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9539</v>
+        <v>0.7372</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2656</v>
+        <v>0.1106</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6883</v>
+        <v>0.6267</v>
       </c>
       <c r="V3" t="n">
         <v>0.7395</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.2724</v>
+        <v>4.6827</v>
       </c>
       <c r="E4" t="n">
-        <v>6.8739</v>
+        <v>6.3151</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.6015</v>
+        <v>-1.6323</v>
       </c>
       <c r="G4" t="n">
         <v>4.4229</v>
@@ -766,13 +766,13 @@
         <v>0.87</v>
       </c>
       <c r="S4" t="n">
-        <v>1.067</v>
+        <v>0.4774</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2281</v>
+        <v>0.6694</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1612</v>
+        <v>-0.192</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. GIL GARCIA</t>
+          <t>J. ZIDEK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.368</v>
+        <v>3.9409</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1638</v>
+        <v>3.9869</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2042</v>
+        <v>-0.046</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7155</v>
+        <v>1.3106</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8788</v>
+        <v>0.3161</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1633</v>
+        <v>0.9945000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6878</v>
+        <v>2.7284</v>
       </c>
       <c r="K5" t="n">
-        <v>1.6607</v>
+        <v>0.949</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.9729</v>
+        <v>1.7794</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0277</v>
+        <v>-1.4178</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7819</v>
+        <v>-0.6328</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8096</v>
+        <v>-0.7849</v>
       </c>
       <c r="P5" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="S5" t="n">
-        <v>0.435</v>
+        <v>0.6303</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3461</v>
+        <v>0.1286</v>
       </c>
       <c r="U5" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.5017</v>
       </c>
       <c r="V5" t="n">
         <v>1.13</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. ZIDEK</t>
+          <t>G. GIL GARCIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.3089</v>
+        <v>3.4365</v>
       </c>
       <c r="E6" t="n">
-        <v>3.5399</v>
+        <v>2.2323</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.231</v>
+        <v>1.2042</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3106</v>
+        <v>0.7155</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3161</v>
+        <v>0.8788</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9945000000000001</v>
+        <v>-0.1633</v>
       </c>
       <c r="J6" t="n">
-        <v>2.7284</v>
+        <v>0.6878</v>
       </c>
       <c r="K6" t="n">
-        <v>0.949</v>
+        <v>1.6607</v>
       </c>
       <c r="L6" t="n">
-        <v>1.7794</v>
+        <v>-0.9729</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4178</v>
+        <v>0.0277</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6328</v>
+        <v>-0.7819</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7849</v>
+        <v>0.8096</v>
       </c>
       <c r="P6" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0017</v>
+        <v>0.5034999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3184</v>
+        <v>0.4146</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3168</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="V6" t="n">
         <v>1.13</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.2819</v>
+        <v>3.0459</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1517</v>
+        <v>0.8849</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1302</v>
+        <v>2.161</v>
       </c>
       <c r="G7" t="n">
         <v>1.7953</v>
@@ -1000,13 +1000,13 @@
         <v>1.305</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1816</v>
+        <v>-0.0544</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2656</v>
+        <v>-0.0012</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.0532</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2198</v>
+        <v>0.3817</v>
       </c>
       <c r="E8" t="n">
-        <v>1.6095</v>
+        <v>1.833</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3897</v>
+        <v>-1.4513</v>
       </c>
       <c r="G8" t="n">
         <v>0.0369</v>
@@ -1078,13 +1078,13 @@
         <v>1.5225</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0959</v>
+        <v>0.2578</v>
       </c>
       <c r="T8" t="n">
-        <v>0.08409999999999999</v>
+        <v>0.3076</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0118</v>
+        <v>-0.0499</v>
       </c>
       <c r="V8" t="n">
         <v>0.7395</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0796</v>
+        <v>-0.144</v>
       </c>
       <c r="E9" t="n">
-        <v>2.5353</v>
+        <v>2.3118</v>
       </c>
       <c r="F9" t="n">
         <v>-2.4558</v>
@@ -1156,10 +1156,10 @@
         <v>1.0875</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0805</v>
+        <v>-0.143</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2656</v>
+        <v>0.0421</v>
       </c>
       <c r="U9" t="n">
         <v>-0.1851</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2658</v>
+        <v>-1.0924</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4266</v>
+        <v>-0.3149</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8391999999999999</v>
+        <v>-0.7775</v>
       </c>
       <c r="G10" t="n">
         <v>-1.4527</v>
@@ -1234,13 +1234,13 @@
         <v>1.0875</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5309</v>
+        <v>-0.3575</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4675</v>
+        <v>-0.3557</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0635</v>
+        <v>-0.0018</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3698</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5559</v>
+        <v>-1.2215</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.3262</v>
+        <v>-2.146</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7703</v>
+        <v>0.9245</v>
       </c>
       <c r="G11" t="n">
         <v>0.3674</v>
@@ -1312,13 +1312,13 @@
         <v>0.6525</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4008</v>
+        <v>-0.0664</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2055</v>
+        <v>-0.0252</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1953</v>
+        <v>-0.0412</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.4909</v>
+        <v>-1.8165</v>
       </c>
       <c r="E12" t="n">
-        <v>1.3172</v>
+        <v>1.6525</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.8081</v>
+        <v>-3.4691</v>
       </c>
       <c r="G12" t="n">
         <v>0.1411</v>
@@ -1390,13 +1390,13 @@
         <v>0.435</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8495</v>
+        <v>-0.1751</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.399</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4505</v>
+        <v>-0.1115</v>
       </c>
       <c r="V12" t="n">
         <v>-1.13</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.4181</v>
+        <v>-4.8805</v>
       </c>
       <c r="E13" t="n">
         <v>-4.0816</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3365</v>
+        <v>-0.7989000000000001</v>
       </c>
       <c r="G13" t="n">
         <v>-1.9312</v>
@@ -1468,13 +1468,13 @@
         <v>0.6525</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2107</v>
+        <v>0.7484</v>
       </c>
       <c r="T13" t="n">
         <v>0.4831</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7276</v>
+        <v>0.2653</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>18.0617</v>
+        <v>18.4041</v>
       </c>
       <c r="E14" t="n">
-        <v>22.3903</v>
+        <v>22.7327</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.328799999999999</v>
+        <v>-4.3286</v>
       </c>
       <c r="G14" t="n">
         <v>15.7777</v>
@@ -1534,7 +1534,7 @@
         <v>-12.6403</v>
       </c>
       <c r="O14" t="n">
-        <v>1.6136</v>
+        <v>1.613599999999999</v>
       </c>
       <c r="P14" t="n">
         <v>-2.1751</v>
@@ -1546,10 +1546,10 @@
         <v>10.875</v>
       </c>
       <c r="S14" t="n">
-        <v>3.544900000000001</v>
+        <v>3.8876</v>
       </c>
       <c r="T14" t="n">
-        <v>2.030899999999999</v>
+        <v>2.3735</v>
       </c>
       <c r="U14" t="n">
         <v>1.5139</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1829</v>
+        <v>1.3646</v>
       </c>
       <c r="E15" t="n">
-        <v>2.284</v>
+        <v>1.5017</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1011</v>
+        <v>-0.137</v>
       </c>
       <c r="G15" t="n">
         <v>-0.3464</v>
@@ -1624,13 +1624,13 @@
         <v>1.305</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1817</v>
+        <v>0.3635</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0227</v>
+        <v>0.2403</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1591</v>
+        <v>0.1232</v>
       </c>
       <c r="V15" t="n">
         <v>1.13</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3795</v>
+        <v>-0.2497</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0169</v>
+        <v>0.9051</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.3964</v>
+        <v>-1.1549</v>
       </c>
       <c r="G16" t="n">
         <v>-1.7391</v>
@@ -1702,13 +1702,13 @@
         <v>0.87</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.07530000000000001</v>
+        <v>0.0544</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3461</v>
+        <v>0.2343</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4214</v>
+        <v>-0.18</v>
       </c>
       <c r="V16" t="n">
         <v>0.5649999999999999</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. CRUZ UCEDA</t>
+          <t>C. DIAZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7717000000000001</v>
+        <v>-1.1181</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2033</v>
+        <v>1.7947</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.975</v>
+        <v>-2.9128</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.8076</v>
+        <v>-2.5355</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0762</v>
+        <v>-2.3323</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8837</v>
+        <v>-0.2032</v>
       </c>
       <c r="J17" t="n">
-        <v>2.373</v>
+        <v>1.0267</v>
       </c>
       <c r="K17" t="n">
-        <v>2.6009</v>
+        <v>-0.638</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.2279</v>
+        <v>1.6647</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.1806</v>
+        <v>-3.5622</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.5247</v>
+        <v>-1.6943</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6558</v>
+        <v>-1.8679</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.9576</v>
+        <v>0.87</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.2626</v>
+        <v>-1.0875</v>
       </c>
       <c r="R17" t="n">
-        <v>1.305</v>
+        <v>1.9576</v>
       </c>
       <c r="S17" t="n">
-        <v>1.9112</v>
+        <v>-0.6647999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8977000000000001</v>
+        <v>-0.5996</v>
       </c>
       <c r="U17" t="n">
-        <v>1.0135</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>0.0822</v>
+        <v>1.2122</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1952</v>
+        <v>2.4552</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.113</v>
+        <v>-1.243</v>
       </c>
     </row>
     <row r="18">
@@ -1813,10 +1813,10 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2391</v>
+        <v>-1.4626</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0167</v>
+        <v>1.7931</v>
       </c>
       <c r="F18" t="n">
         <v>-3.2558</v>
@@ -1858,10 +1858,10 @@
         <v>1.305</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0445</v>
+        <v>-0.268</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2896</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="U18" t="n">
         <v>-0.3341</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. DIAZ RODRIGUEZ</t>
+          <t>J. GARCIA SANCHEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.8798</v>
+        <v>-1.5881</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4594</v>
+        <v>2.6422</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.3392</v>
+        <v>-4.2304</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.5355</v>
+        <v>-2.1196</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.3323</v>
+        <v>-1.1649</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2032</v>
+        <v>-0.9546</v>
       </c>
       <c r="J19" t="n">
-        <v>1.0267</v>
+        <v>1.6284</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.638</v>
+        <v>1.7583</v>
       </c>
       <c r="L19" t="n">
-        <v>1.6647</v>
+        <v>-0.1298</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.5622</v>
+        <v>-3.748</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.6943</v>
+        <v>-2.9232</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.8679</v>
+        <v>-0.8248</v>
       </c>
       <c r="P19" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9576</v>
+        <v>2.1751</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.4265</v>
+        <v>-0.4431</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9349</v>
+        <v>-0.1586</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4916</v>
+        <v>-0.2845</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2122</v>
+        <v>-0.113</v>
       </c>
       <c r="W19" t="n">
-        <v>2.4552</v>
+        <v>2.2599</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.243</v>
+        <v>-2.3729</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. GARCIA SANCHEZ</t>
+          <t>I. CRUZ UCEDA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.784</v>
+        <v>-1.8339</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0834</v>
+        <v>-0.3555</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.8675</v>
+        <v>-1.4784</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.1196</v>
+        <v>-0.8076</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.1649</v>
+        <v>0.0762</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9546</v>
+        <v>-0.8837</v>
       </c>
       <c r="J20" t="n">
-        <v>1.6284</v>
+        <v>2.373</v>
       </c>
       <c r="K20" t="n">
-        <v>1.7583</v>
+        <v>2.6009</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.1298</v>
+        <v>-0.2279</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.748</v>
+        <v>-3.1806</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.9232</v>
+        <v>-2.5247</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8248</v>
+        <v>-0.6558</v>
       </c>
       <c r="P20" t="n">
-        <v>1.0875</v>
+        <v>-1.9576</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0875</v>
+        <v>-3.2626</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1751</v>
+        <v>1.305</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.639</v>
+        <v>0.849</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7174</v>
+        <v>0.3389</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.9216</v>
+        <v>0.5101</v>
       </c>
       <c r="V20" t="n">
+        <v>0.0822</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.1952</v>
+      </c>
+      <c r="X20" t="n">
         <v>-0.113</v>
-      </c>
-      <c r="W20" t="n">
-        <v>2.2599</v>
-      </c>
-      <c r="X20" t="n">
-        <v>-2.3729</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.6612</v>
+        <v>-3.4004</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0224</v>
+        <v>-1.9107</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6388</v>
+        <v>-1.4898</v>
       </c>
       <c r="G21" t="n">
         <v>-0.5956</v>
@@ -2092,13 +2092,13 @@
         <v>1.305</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.995</v>
+        <v>-0.7342</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8099</v>
+        <v>-0.6982</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1851</v>
+        <v>-0.0361</v>
       </c>
       <c r="V21" t="n">
         <v>-0.113</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. GODSPOWER JOHNSON</t>
+          <t>P. KRUTOUS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.3686</v>
+        <v>-3.7914</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.6171</v>
+        <v>0.5750999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.7515</v>
+        <v>-4.3664</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.095</v>
+        <v>-2.7136</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.0255</v>
+        <v>-0.0823</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.0694</v>
+        <v>-2.6312</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.0127</v>
+        <v>1.9954</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.3441</v>
+        <v>3.5039</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6686</v>
+        <v>-1.5084</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.0823</v>
+        <v>-4.709</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6814</v>
+        <v>-3.5862</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.4009</v>
+        <v>-1.1228</v>
       </c>
       <c r="P22" t="n">
-        <v>1.305</v>
+        <v>0.435</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R22" t="n">
-        <v>1.305</v>
+        <v>1.5225</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4487</v>
+        <v>-0.6395999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6044</v>
+        <v>-0.3329</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1557</v>
+        <v>-0.3067</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.13</v>
+        <v>-0.8732</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.13</v>
+        <v>-0.8732</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P. KRUTOUS</t>
+          <t>J. GODSPOWER JOHNSON</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.1606</v>
+        <v>-4.4919</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.0955</v>
+        <v>-2.6171</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.0651</v>
+        <v>-1.8748</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.7136</v>
+        <v>-4.095</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0823</v>
+        <v>-2.0255</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.6312</v>
+        <v>-2.0694</v>
       </c>
       <c r="J23" t="n">
-        <v>1.9954</v>
+        <v>-2.0127</v>
       </c>
       <c r="K23" t="n">
-        <v>3.5039</v>
+        <v>-1.3441</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.5084</v>
+        <v>-0.6686</v>
       </c>
       <c r="M23" t="n">
-        <v>-4.709</v>
+        <v>-2.0823</v>
       </c>
       <c r="N23" t="n">
-        <v>-3.5862</v>
+        <v>-0.6814</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.1228</v>
+        <v>-1.4009</v>
       </c>
       <c r="P23" t="n">
-        <v>0.435</v>
+        <v>1.305</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5225</v>
+        <v>1.305</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.0089</v>
+        <v>-0.572</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0034</v>
+        <v>-0.6044</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.0055</v>
+        <v>0.0324</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.8732</v>
+        <v>-1.13</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.8732</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-18.0616</v>
+        <v>-16.5715</v>
       </c>
       <c r="E24" t="n">
-        <v>4.328699999999999</v>
+        <v>4.3286</v>
       </c>
       <c r="F24" t="n">
-        <v>-22.3904</v>
+        <v>-20.9003</v>
       </c>
       <c r="G24" t="n">
         <v>-15.7778</v>
@@ -2317,7 +2317,7 @@
         <v>-8.3713</v>
       </c>
       <c r="P24" t="n">
-        <v>2.1748</v>
+        <v>2.174799999999999</v>
       </c>
       <c r="Q24" t="n">
         <v>-10.8752</v>
@@ -2326,22 +2326,22 @@
         <v>13.0502</v>
       </c>
       <c r="S24" t="n">
-        <v>-3.545</v>
+        <v>-2.0548</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.5139</v>
+        <v>-1.5141</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.031</v>
+        <v>-0.5408999999999999</v>
       </c>
       <c r="V24" t="n">
         <v>-0.9140999999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>5.691199999999999</v>
+        <v>5.6912</v>
       </c>
       <c r="X24" t="n">
-        <v>-6.6053</v>
+        <v>-6.605300000000001</v>
       </c>
     </row>
   </sheetData>
